--- a/docs/cells/flood_real_estate/proposed/damage_curve_records_flood_real_estate__model_v0_1__docs_r1.xlsx
+++ b/docs/cells/flood_real_estate/proposed/damage_curve_records_flood_real_estate__model_v0_1__docs_r1.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="curve_records" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="reference_buildings" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="sources" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="claims" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="parameter_tiers" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="value_crosswalk" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="known_answer_tests" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="curve_records" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reference_buildings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="claims" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="parameter_tiers" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="value_crosswalk" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="known_answer_tests" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5573,7 +5573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -6620,6 +6620,93 @@
       <c r="Q12" t="inlineStr">
         <is>
           <t>Retrieved 2026-10-11; file sha256 values recorded in the NSI sample CSV. Defaults identical across the three counties.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FRE-S012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FEMA. OpenFEMA FIMA NFIP Redacted Claims, dataset NfipClaims version 3 (API).</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.fema.gov/api/open/v3/NfipClaims</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Three filtered pulls (one-floor slab buildings with exterior water depth &gt; 0): single-family with damage (95,435), non-residential with damage (10,180), single-family with zero damage (1,006). Filters, record counts and sha256 of the cached pulls in NFIP_CLAIMS_PULL_MANIFEST_flood_real_estate__model_v0_1__docs_r1.json</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>government dataset</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>validation_only</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>flood_inundation_contact</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>T1_claims_or_field_calibrated</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>adjuster-assessed building damage amount and building replacement cost per paid NFIP claim, with exterior water depth above grade, cause of damage and flood zone</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Compare the proposed curves with the mean damage ratio of analogue claims by depth band, as a reasonableness check and as evidence for curve selection.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Refit or calibrate the curves to the claims; treat the claims as nationally representative (95% of the house claims are from Gulf states); treat the damage ratio as replacement-cost-new repair cost for the reference buildings.</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>adopt_with_limits</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Retrieved by script (scripts/reference_helpers/flood_real_estate_nfip_claims_check.py); raw pulls cached in gitignored build/nfip_claims. Losses 2008-2026, all but 103 from 2016 onward. Results in NFIP_CLAIMS_CHECK_flood_real_estate__model_v0_1__docs_r1.md.</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -8379,6 +8466,408 @@
       <c r="M26" t="inlineStr">
         <is>
           <t>Owner asks to reproduce Hazus exactly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>FRE-C026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>flood_inundation_contact</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>The FEMA freshwater curves agree with NFIP claims within about 6 points for the house at 2-6 ft above the floor and for the commercial analogue at 0-10 ft; both curves sit below the claims at shallow depth.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>direct_observation</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>FRE-S012;FRE-S002</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>NFIP_CLAIMS_COMPARISON_flood_real_estate__model_v0_1__docs_r1.csv freshwater rows</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>T1_claims_or_field_calibrated</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>freshwater curve validation</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>adopt</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Use as evidence that the freshwater records are reasonable for slab buildings.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Treat as calibration or extend to building types not compared.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>House 2-6 ft differences -0.049 to +0.052; commercial 0-10 ft -0.056 to -0.018 (claims-weighted band means).</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>A rerun on a newer pull or a changed curve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>FRE-C027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>flood_inundation_contact</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>The NACCS coastal house curve (5A) is 12-23 points below NFIP coastal-surge claims in the first 2 ft above the floor, where 72% of the compared coastal house claims fall; the claims sit near the NACCS upper bound.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>direct_observation</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>FRE-S012;FRE-S004</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>NFIP_CLAIMS_COMPARISON_flood_real_estate__model_v0_1__docs_r1.csv house coastal rows</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>T1_claims_or_field_calibrated</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>coastal curve validation</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>adopt</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Record that the coastal house record understates claims at shallow depth.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Conclude NACCS is wrong in its own study region (only 0.7% of the house claims are from the Northeast).</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0-0.5 ft -0.226, 0.5-1 ft -0.181, 1-2 ft -0.125.</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>A rerun, or claims evidence from the North Atlantic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>FRE-C028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>flood_inundation_contact</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>The NACCS coastal commercial curve (prototype 2) is 6-12 points above NFIP coastal-surge claims for the commercial analogue from 1 ft above the floor.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>direct_observation</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>FRE-S012;FRE-S004</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>NFIP_CLAIMS_COMPARISON_flood_real_estate__model_v0_1__docs_r1.csv commercial coastal rows</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>T1_claims_or_field_calibrated</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>coastal curve validation</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>adopt</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Record that the coastal commercial record overstates claims above 1 ft.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Extend to the office target (the analogue is one-floor business occupancies).</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1-2 ft +0.060 rising to +0.115 at 4-5 ft; 1,163 claims.</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>A rerun, or an office-specific comparison.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>FRE-C029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>flood_inundation_contact</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Applied to the same coastal-surge claims, the FEMA freshwater curves are 8-12 points below the house claims at 0-2 ft and within 7 points at 2-6 ft, and 7-10 points below the commercial claims at 0-6 ft.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>direct_observation</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>FRE-S012;FRE-S002</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>NFIP_CLAIMS_COMPARISON_flood_real_estate__model_v0_1__docs_r1.csv columns fema_freshwater_*</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>T1_claims_or_field_calibrated</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>coastal curve choice</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>defer</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Use as evidence for the coastal source choice (D-FRE-18 revisit trigger).</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Switch the coastal records without a recorded owner decision.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Closer than NACCS for the house; about as far from the claims as NACCS for commercial, on the other side.</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Owner coastal decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>FRE-C030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>flood_inundation_contact</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NFIP coastal-surge claims match freshwater claims for the house analogue at the same depth (within 5 points at 0-6 ft), but run 2-11 points higher for the commercial analogue.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>direct_observation</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>FRE-S012</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>NFIP_CLAIMS_COMPARISON_flood_real_estate__model_v0_1__docs_r1.csv claims_mean_dr</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>T1_claims_or_field_calibrated</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>water-type distinction</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>adopt</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Record that saline surge adds little damage for slab houses in the claims but does for commercial analogues.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Infer a salinity multiplier.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>House 0-6 ft: coastal minus freshwater -0.046 to +0.014; commercial +0.023 to +0.113.</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>A rerun or a salinity-specific study.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>FRE-C031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>flood_inundation_contact</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>The shallow-depth gap for the house is sensitive to the assumed first-floor height: for claims 0.5-2.0 ft above grade, the freshwater curve is 3 points below the claims at a 0 ft floor height and 10 points below at the reference 0.75 ft.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>engineering_inference</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>FRE-S012;FRE-S011</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>NFIP_CLAIMS_SENSITIVITY_flood_real_estate__model_v0_1__docs_r1.csv floor-height rows</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>T3_engineering_proxy_or_adjacent_empirical</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>first_floor_height.RE_RES_SFD_1S_SLAB</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>adopt</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Record floor height as the main open sensitivity behind the shallow gap.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Change the reference floor height from this comparison alone.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Claims mean 0.269; curve 0.238 / 0.214 / 0.166 / 0.141 at 0 / 0.25 / 0.75 / 1 ft. Adding zero-damage claims or splitting by settlement basis moves the claims mean by under 1 point.</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Observed floor heights for the claims, or Hazard's grade-to-floor conversion.</t>
         </is>
       </c>
     </row>

--- a/docs/cells/flood_real_estate/proposed/damage_curve_records_flood_real_estate__model_v0_1__docs_r1.xlsx
+++ b/docs/cells/flood_real_estate/proposed/damage_curve_records_flood_real_estate__model_v0_1__docs_r1.xlsx
@@ -5573,7 +5573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -6707,6 +6707,93 @@
       <c r="Q13" t="inlineStr">
         <is>
           <t>Retrieved by script (scripts/reference_helpers/flood_real_estate_nfip_claims_check.py); raw pulls cached in gitignored build/nfip_claims. Losses 2008-2026, all but 103 from 2016 onward. Results in NFIP_CLAIMS_CHECK_flood_real_estate__model_v0_1__docs_r1.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FRE-S013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Hazard_Modeling. Real-estate reference profiles r1 (reference_candidates.yml and generated profile views), handoff of 2026-10-16.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://github.com/aamani-ai/Hazard_Modeling/blob/8b0d61c88fbcf85daa1c098516cee22398cdb524/docs/plans/_cross_cutting/real_estate_conus/reference_candidates.yml</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>commit 8b0d61c88fbcf85daa1c098516cee22398cdb524; reference_candidates.yml git blob a74fb72b0a2edce593b5505e0fd8852f4c0253f8; profiles re_house_1s_wood_slab, re_warehouse_1s_steel_slab, re_office_3s_slab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>internal design input</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>selector_archetype;exposure_or_value</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>flood_inundation_contact;flood_wave_velocity</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>T4_placeholder_or_expert_judgment</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>declared physical target per reference building: occupancy, stories, foundation, first-floor height, construction, services, interiors, included scope and a screening replacement budget</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Bind curve records to the profiles and check which profile fields change curve selection.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Treat the profiles as observed buildings or the budgets as qualified coverage of a curve's denominator.</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>adopt</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Declared design, not evidence of damage. Binding in PROFILE_BINDING_flood_real_estate__model_v0_1__docs_r1.md.</t>
         </is>
       </c>
     </row>

--- a/docs/cells/flood_real_estate/proposed/damage_curve_records_flood_real_estate__model_v0_1__docs_r1.xlsx
+++ b/docs/cells/flood_real_estate/proposed/damage_curve_records_flood_real_estate__model_v0_1__docs_r1.xlsx
@@ -6808,7 +6808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -8955,6 +8955,341 @@
       <c r="M32" t="inlineStr">
         <is>
           <t>Observed floor heights for the claims, or Hazard's grade-to-floor conversion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>FRE-C032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>flood_inundation_contact</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Hazus DF 431 (COM4, Average Prof/Tech Services, Structure, USACE Galveston) is identical at all 29 knots (-4 to 24 ft) in the Pollack compilation, USACE go-consequences and the Hazus 6.1 extract.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>direct_observation</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>FRE-S001;FRE-S003;FRE-S005;FRE-S010</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>OFFICE_FLOOD_RESEARCH_flood_real_estate__model_v0_1__docs_r1.md §2; haz_fl_dept.csv DmgFnId 431 (flBldgStructDmgFn); occtypes.json COM4 structure; flBldgStrucDmgFn ID 431</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>T2_public_lab_standard_or_physics</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>office freshwater ordinate integrity</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>adopt</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Use the DF 431 ordinates for an office record.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Use contents curve 431 (IND3) by mistake; the ID is reused across tables.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Three independent carriers agree.</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>A newer Hazus release changes DF 431.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>FRE-C033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>flood_inundation_contact</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>FEMA's default structure curve for COM4 is DF 431 at every height class (under 4, 4-7, over 7 storeys), with or without basement, and for riverine, coastal A and coastal V hazards.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>direct_observation</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>FRE-S010;FRE-S002</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Hazus 6.1 flBldgStructDmgFinal rows C4LN, C4LB, C4MN, C4MB, C4HN, C4HB (HazardR, HazardCA, HazardCV = 1); SOoccupId_Occ_Xref</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>T2_public_lab_standard_or_physics</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>office curve selection</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>adopt</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>DF 431 matches every key FEMA selects on for a three-storey office without basement, in all flood zones.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Read FEMA's assignment as evidence that height does not matter physically.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>FEMA does not adjust commercial curves for height.</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>A Hazus release with height-specific commercial defaults.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>FRE-C034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>flood_inundation_contact</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>In NFIP business claims (occupancy 4, 6, 18; slab), damage as a share of the building falls with the number of floors: at matched depth bands two floors show about 0.75 of the one-floor ratio (freshwater; 0.67 coastal) and three or more floors about 0.5 (freshwater, up to 3 ft).</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>direct_observation</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>FRE-S012</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>NFIP_CLAIMS_BY_STOREYS_flood_real_estate__model_v0_1__docs_r1.csv; OFFICE_FLOOD_RESEARCH_flood_real_estate__model_v0_1__docs_r1.md §4</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>T1_claims_or_field_calibrated</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>office height effect</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>adopt</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Record that a whole-building curve for one-floor stock overstates multi-floor buildings; use the ratio as a stated sensitivity.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Apply the ratio as a calibration factor; read 'three or more' as three storeys.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Freshwater claims mean 14.4% (1 floor, 6,529), 11.3% (2, 1,628), 6.3% (3+, 228).</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Office-specific or height-specific claims evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>FRE-C035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>flood_inundation_contact</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>On the same NFIP business claims, DF 431 is within 1 point of one-floor freshwater claims and about 3.5 points (x1.6) above three-or-more-floor freshwater claims; in coastal surge it is within 2-5 points of two-floor and taller claims, while NACCS prototype 2 is 11-13 points above them.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>direct_observation</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>FRE-S012;FRE-S004</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>NFIP_CLAIMS_BY_STOREYS_flood_real_estate__model_v0_1__docs_r1.csv; OFFICE_FLOOD_RESEARCH_flood_real_estate__model_v0_1__docs_r1.md §4</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>T1_claims_or_field_calibrated</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>office curve validation</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>adopt</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Use as evidence for the office freshwater and coastal choices.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Treat as calibration of either curve.</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Coastal 2 floors: claims 12.5%, DF 431 14.3%, NACCS P2 23.4%; 3+ floors: 5.9%, 10.6%, 19.2% (46 claims).</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Owner office and coastal decisions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>FRE-C036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>flood_inundation_contact</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Other Hazus office structure curves do not fit better: DF 438 (Big Office Commercial) is within 2-3 points of DF 431 on the claims, DF 466 (Wilmington Office Building) is 21-34 points above every claims group, and the New Orleans office curves (DF 444-462) reach 65-100% by 3 ft.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>direct_observation</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>FRE-S010;FRE-S012</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>OFFICE_FLOOD_RESEARCH_flood_real_estate__model_v0_1__docs_r1.md §2, §4</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>T1_claims_or_field_calibrated</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>office curve alternatives</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>reject</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Record the alternatives and why they are not proposed.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Use a regional office curve CONUS-wide.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Galveston DF 438 is the only close alternative; it is not FEMA's default and fits no better.</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>A height- or size-specific office curve is found.</t>
         </is>
       </c>
     </row>

--- a/docs/cells/flood_real_estate/proposed/damage_curve_records_flood_real_estate__model_v0_1__docs_r1.xlsx
+++ b/docs/cells/flood_real_estate/proposed/damage_curve_records_flood_real_estate__model_v0_1__docs_r1.xlsx
@@ -6808,7 +6808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -9290,6 +9290,73 @@
       <c r="M37" t="inlineStr">
         <is>
           <t>A height- or size-specific office curve is found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>FRE-C037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>flood_inundation_contact</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>For the warehouse there is little coastal claims evidence: on 14 NFIP coastal-surge claims with a warehouse building description at 1-3 ft above the floor (mean damage 14%), Hazus DF 341 reads 7% and NACCS prototype 3 reads 26%; on all 1-floor business coastal claims DF 341 is 11-13 points below and NACCS prototype 3 1-13 points above.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>direct_observation</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>FRE-S012;FRE-S004;FRE-S010</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>NFIP pulls in build/nfip_claims (nonres.json); computed 2026-10-16 with the v0.1 records</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>T1_claims_or_field_calibrated</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>warehouse coastal curve choice</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>adopt</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Record that neither curve fits the few coastal warehouse claims: DF 341 low, NACCS prototype 3 high.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Read 14 claims as calibration of either curve.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1-floor business coastal claims (all occupancies 4, 6, 18): 13.2% / 19.9% / 26.7% at 0-1 / 1-3 / 3-6 ft vs DF 341 2.4% / 7.5% / 13.4% and NACCS P3 12.0% / 26.5% / 40.0%.</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>More coastal warehouse claims or a warehouse-specific coastal study.</t>
         </is>
       </c>
     </row>
